--- a/docs/downloads/20261001_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20261001_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,10 @@
     <col width="9" customWidth="1" min="37" max="37"/>
     <col width="9" customWidth="1" min="38" max="38"/>
     <col width="9" customWidth="1" min="39" max="39"/>
-    <col width="42" customWidth="1" min="40" max="40"/>
+    <col width="9" customWidth="1" min="40" max="40"/>
+    <col width="9" customWidth="1" min="41" max="41"/>
+    <col width="9" customWidth="1" min="42" max="42"/>
+    <col width="42" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -579,8 +582,11 @@
       <c r="AH3" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="AK3" s="4" t="n">
+      <c r="AK3" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="AN3" s="4" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -767,22 +773,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AK4" s="6" t="inlineStr">
+      <c r="AK4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AL4" s="6" t="inlineStr">
+      <c r="AL4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AM4" s="6" t="inlineStr">
+      <c r="AM4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="AN4" s="5" t="inlineStr">
+      <c r="AN4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AO4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AP4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AQ4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -922,18 +943,29 @@
         <f>AI5/$D$5</f>
         <v/>
       </c>
-      <c r="AK5" s="12">
+      <c r="AK5" s="10">
         <f>AL5-AI5</f>
         <v/>
       </c>
-      <c r="AL5" s="12" t="n">
+      <c r="AL5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AM5" s="11">
         <f>AL5/$D$5</f>
         <v/>
       </c>
-      <c r="AN5" s="8" t="inlineStr">
+      <c r="AN5" s="12">
+        <f>AO5-AL5</f>
+        <v/>
+      </c>
+      <c r="AO5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="AP5" s="13">
+        <f>AO5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -1073,18 +1105,29 @@
         <f>AI6/$D$6</f>
         <v/>
       </c>
-      <c r="AK6" s="12">
+      <c r="AK6" s="10">
         <f>AL6-AI6</f>
         <v/>
       </c>
-      <c r="AL6" s="12" t="n">
+      <c r="AL6" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="AM6" s="13">
+      <c r="AM6" s="11">
         <f>AL6/$D$6</f>
         <v/>
       </c>
-      <c r="AN6" s="8" t="inlineStr">
+      <c r="AN6" s="12">
+        <f>AO6-AL6</f>
+        <v/>
+      </c>
+      <c r="AO6" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP6" s="13">
+        <f>AO6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AQ6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -1224,18 +1267,29 @@
         <f>AI7/$D$7</f>
         <v/>
       </c>
-      <c r="AK7" s="12">
+      <c r="AK7" s="10">
         <f>AL7-AI7</f>
         <v/>
       </c>
-      <c r="AL7" s="12" t="n">
+      <c r="AL7" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="AM7" s="13">
+      <c r="AM7" s="11">
         <f>AL7/$D$7</f>
         <v/>
       </c>
-      <c r="AN7" s="8" t="inlineStr">
+      <c r="AN7" s="12">
+        <f>AO7-AL7</f>
+        <v/>
+      </c>
+      <c r="AO7" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="AP7" s="13">
+        <f>AO7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AQ7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -1375,18 +1429,29 @@
         <f>AI8/$D$8</f>
         <v/>
       </c>
-      <c r="AK8" s="12">
+      <c r="AK8" s="10">
         <f>AL8-AI8</f>
         <v/>
       </c>
-      <c r="AL8" s="12" t="n">
+      <c r="AL8" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AM8" s="11">
         <f>AL8/$D$8</f>
         <v/>
       </c>
-      <c r="AN8" s="8" t="inlineStr">
+      <c r="AN8" s="12">
+        <f>AO8-AL8</f>
+        <v/>
+      </c>
+      <c r="AO8" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP8" s="13">
+        <f>AO8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AQ8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1526,18 +1591,29 @@
         <f>AI9/$D$9</f>
         <v/>
       </c>
-      <c r="AK9" s="12">
+      <c r="AK9" s="10">
         <f>AL9-AI9</f>
         <v/>
       </c>
-      <c r="AL9" s="12" t="n">
+      <c r="AL9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AM9" s="11">
         <f>AL9/$D$9</f>
         <v/>
       </c>
-      <c r="AN9" s="8" t="inlineStr">
+      <c r="AN9" s="12">
+        <f>AO9-AL9</f>
+        <v/>
+      </c>
+      <c r="AO9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="13">
+        <f>AO9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AQ9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1667,18 +1743,29 @@
         <f>AI10/$D$10</f>
         <v/>
       </c>
-      <c r="AK10" s="12">
+      <c r="AK10" s="10">
         <f>AL10-AI10</f>
         <v/>
       </c>
-      <c r="AL10" s="12" t="n">
+      <c r="AL10" s="10" t="n">
         <v>359</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AM10" s="11">
         <f>AL10/$D$10</f>
         <v/>
       </c>
-      <c r="AN10" s="8" t="inlineStr">
+      <c r="AN10" s="12">
+        <f>AO10-AL10</f>
+        <v/>
+      </c>
+      <c r="AO10" s="12" t="n">
+        <v>359</v>
+      </c>
+      <c r="AP10" s="13">
+        <f>AO10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AQ10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
@@ -1776,21 +1863,32 @@
         <f>AI11/$D$11</f>
         <v/>
       </c>
-      <c r="AK11" s="12">
+      <c r="AK11" s="10">
         <f>AL11-AI11</f>
         <v/>
       </c>
-      <c r="AL11" s="12" t="n">
+      <c r="AL11" s="10" t="n">
         <v>83</v>
       </c>
-      <c r="AM11" s="13">
+      <c r="AM11" s="11">
         <f>AL11/$D$11</f>
         <v/>
       </c>
-      <c r="AN11" s="8" t="inlineStr"/>
+      <c r="AN11" s="12">
+        <f>AO11-AL11</f>
+        <v/>
+      </c>
+      <c r="AO11" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="AP11" s="13">
+        <f>AO11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="AB3:AD3"/>
@@ -1800,6 +1898,7 @@
     <mergeCell ref="V3:X3"/>
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AJ3"/>
+    <mergeCell ref="AN3:AP3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="P3:R3"/>
   </mergeCells>
